--- a/academia/mestrado/cronograma-1sem.xlsx
+++ b/academia/mestrado/cronograma-1sem.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
   <si>
     <t>D</t>
   </si>
@@ -89,6 +89,36 @@
   </si>
   <si>
     <t>Congresso Simulado</t>
+  </si>
+  <si>
+    <t>Aula (modelos)</t>
+  </si>
+  <si>
+    <t>Aula (IPC)</t>
+  </si>
+  <si>
+    <t>Aula (Objetos Distribuídos)</t>
+  </si>
+  <si>
+    <t>Aula (Sistemas de arq. distr.)</t>
+  </si>
+  <si>
+    <t>Seminários</t>
+  </si>
+  <si>
+    <t>Aula (serviços de nomes)</t>
+  </si>
+  <si>
+    <t>Aula (comp. Móvel)</t>
+  </si>
+  <si>
+    <t>Aula (P2P)</t>
+  </si>
+  <si>
+    <t>Aula (WS)</t>
+  </si>
+  <si>
+    <t>Apresentação Trabalhos</t>
   </si>
 </sst>
 </file>
@@ -150,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -332,11 +362,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -345,64 +452,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -703,595 +834,623 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="2.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="2.42578125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="2.42578125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="2.42578125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="11" customWidth="1"/>
-    <col min="10" max="10" width="2.42578125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="11" customWidth="1"/>
-    <col min="12" max="12" width="2.42578125" style="10" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="11" customWidth="1"/>
-    <col min="14" max="14" width="2.42578125" style="10" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="2.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="2.42578125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="2.42578125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="2.42578125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="2.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="2.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="2.42578125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="43.5" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="5"/>
+      <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>20</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="9">
+      <c r="C2" s="6"/>
+      <c r="D2" s="8">
         <v>21</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>22</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="9">
+      <c r="G2" s="6"/>
+      <c r="H2" s="8">
         <v>23</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>24</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="8">
         <v>25</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="8">
         <v>26</v>
       </c>
-      <c r="O2" s="7"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A3" s="4"/>
-      <c r="B3" s="9">
+      <c r="A3" s="23"/>
+      <c r="B3" s="8">
         <v>27</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="9">
+      <c r="C3" s="6"/>
+      <c r="D3" s="8">
         <v>28</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>29</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="9">
+      <c r="G3" s="6"/>
+      <c r="H3" s="8">
         <v>30</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="9">
+      <c r="I3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="8">
         <v>31</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="8">
         <v>1</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="8">
         <v>2</v>
       </c>
-      <c r="O3" s="7"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>3</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="9">
+      <c r="C4" s="6"/>
+      <c r="D4" s="8">
         <v>4</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>5</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="9">
+      <c r="G4" s="6"/>
+      <c r="H4" s="8">
         <v>6</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="9">
+      <c r="I4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="8">
         <v>7</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="8">
         <v>8</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="8">
         <v>9</v>
       </c>
-      <c r="O4" s="7"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="9">
+      <c r="A5" s="23"/>
+      <c r="B5" s="8">
         <v>10</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="14">
+      <c r="C5" s="6"/>
+      <c r="D5" s="13">
         <v>11</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>12</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="9">
+      <c r="G5" s="6"/>
+      <c r="H5" s="8">
         <v>13</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="9">
+      <c r="I5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="8">
         <v>14</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>15</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="9">
+      <c r="M5" s="6"/>
+      <c r="N5" s="8">
         <v>16</v>
       </c>
-      <c r="O5" s="7"/>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="9">
+      <c r="A6" s="23"/>
+      <c r="B6" s="8">
         <v>17</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="18">
+      <c r="C6" s="11"/>
+      <c r="D6" s="17">
         <v>18</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>19</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="9">
+      <c r="G6" s="6"/>
+      <c r="H6" s="13">
         <v>20</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="9">
+      <c r="I6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="8">
         <v>21</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="8">
         <v>22</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="9">
+      <c r="M6" s="6"/>
+      <c r="N6" s="8">
         <v>23</v>
       </c>
-      <c r="O6" s="7"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="9">
+      <c r="A7" s="23"/>
+      <c r="B7" s="8">
         <v>24</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="16">
+      <c r="C7" s="6"/>
+      <c r="D7" s="15">
         <v>25</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>26</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="9">
+      <c r="G7" s="11"/>
+      <c r="H7" s="19">
         <v>27</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="14">
+      <c r="I7" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="24">
         <v>28</v>
       </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="9">
+      <c r="K7" s="14"/>
+      <c r="L7" s="8">
         <v>29</v>
       </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="9">
+      <c r="M7" s="6"/>
+      <c r="N7" s="8">
         <v>30</v>
       </c>
-      <c r="O7" s="7"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>1</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="9">
+      <c r="C8" s="6"/>
+      <c r="D8" s="8">
         <v>2</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>3</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="9">
+      <c r="G8" s="11"/>
+      <c r="H8" s="27">
         <v>4</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="20">
+      <c r="I8" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="25">
         <v>5</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="12">
         <v>6</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="9">
+      <c r="M8" s="6"/>
+      <c r="N8" s="8">
         <v>7</v>
       </c>
-      <c r="O8" s="7"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="9">
+      <c r="A9" s="23"/>
+      <c r="B9" s="8">
         <v>8</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6"/>
+      <c r="D9" s="8">
         <v>9</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>10</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="9">
+      <c r="G9" s="11"/>
+      <c r="H9" s="21">
         <v>11</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="22">
+      <c r="I9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="26">
         <v>12</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="12">
         <v>13</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9">
+      <c r="M9" s="6"/>
+      <c r="N9" s="8">
         <v>14</v>
       </c>
-      <c r="O9" s="7"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="9">
+      <c r="A10" s="23"/>
+      <c r="B10" s="8">
         <v>15</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="14">
+      <c r="C10" s="6"/>
+      <c r="D10" s="13">
         <v>16</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>17</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="9">
+      <c r="G10" s="6"/>
+      <c r="H10" s="15">
         <v>18</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="16">
+      <c r="I10" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="15">
         <v>19</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="9">
+      <c r="K10" s="16"/>
+      <c r="L10" s="8">
         <v>20</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="9">
+      <c r="M10" s="6"/>
+      <c r="N10" s="8">
         <v>21</v>
       </c>
-      <c r="O10" s="7"/>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="9">
+      <c r="A11" s="23"/>
+      <c r="B11" s="8">
         <v>22</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="18">
+      <c r="C11" s="11"/>
+      <c r="D11" s="17">
         <v>23</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>24</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="9">
+      <c r="G11" s="6"/>
+      <c r="H11" s="8">
         <v>25</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="9">
+      <c r="I11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="8">
         <v>26</v>
       </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="9">
+      <c r="K11" s="6"/>
+      <c r="L11" s="8">
         <v>27</v>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9">
+      <c r="M11" s="6"/>
+      <c r="N11" s="8">
         <v>28</v>
       </c>
-      <c r="O11" s="7"/>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="B12" s="9">
+      <c r="A12" s="23"/>
+      <c r="B12" s="8">
         <v>29</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="16">
+      <c r="C12" s="6"/>
+      <c r="D12" s="15">
         <v>30</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>31</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="9">
+      <c r="G12" s="6"/>
+      <c r="H12" s="8">
         <v>1</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="9">
+      <c r="I12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="8">
         <v>2</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="8">
         <v>3</v>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="9">
+      <c r="M12" s="6"/>
+      <c r="N12" s="8">
         <v>4</v>
       </c>
-      <c r="O12" s="7"/>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>5</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="9">
+      <c r="C13" s="6"/>
+      <c r="D13" s="8">
         <v>6</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>7</v>
       </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="9">
+      <c r="G13" s="6"/>
+      <c r="H13" s="13">
         <v>8</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="14">
+      <c r="I13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="13">
         <v>9</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="8">
         <v>10</v>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9">
+      <c r="M13" s="6"/>
+      <c r="N13" s="8">
         <v>11</v>
       </c>
-      <c r="O13" s="7"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="9">
+      <c r="A14" s="23"/>
+      <c r="B14" s="8">
         <v>12</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="9">
+      <c r="C14" s="6"/>
+      <c r="D14" s="8">
         <v>13</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>14</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="9">
+      <c r="G14" s="11"/>
+      <c r="H14" s="19">
         <v>15</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="18">
+      <c r="I14" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="28">
         <v>16</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="12">
         <v>17</v>
       </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="9">
+      <c r="M14" s="6"/>
+      <c r="N14" s="8">
         <v>18</v>
       </c>
-      <c r="O14" s="7"/>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="9">
+      <c r="A15" s="23"/>
+      <c r="B15" s="8">
         <v>19</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="14">
+      <c r="C15" s="6"/>
+      <c r="D15" s="13">
         <v>20</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>21</v>
       </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="9">
+      <c r="G15" s="11"/>
+      <c r="H15" s="27">
         <v>22</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="16">
+      <c r="I15" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="30">
         <v>23</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="K15" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="8">
         <v>24</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9">
+      <c r="M15" s="6"/>
+      <c r="N15" s="8">
         <v>25</v>
       </c>
-      <c r="O15" s="7"/>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="9">
+      <c r="A16" s="23"/>
+      <c r="B16" s="8">
         <v>26</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="18">
+      <c r="C16" s="11"/>
+      <c r="D16" s="17">
         <v>27</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>28</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="9">
+      <c r="G16" s="11"/>
+      <c r="H16" s="21">
         <v>29</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="9">
+      <c r="I16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="17">
         <v>30</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="12">
         <v>1</v>
       </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="9">
+      <c r="M16" s="6"/>
+      <c r="N16" s="8">
         <v>2</v>
       </c>
-      <c r="O16" s="7"/>
+      <c r="O16" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/academia/mestrado/cronograma-1sem.xlsx
+++ b/academia/mestrado/cronograma-1sem.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>D</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>Apresentação Trabalhos</t>
+  </si>
+  <si>
+    <t>Aula (busca heurística)</t>
+  </si>
+  <si>
+    <t>Apresentação do Trabalho (busca)</t>
   </si>
 </sst>
 </file>
@@ -180,7 +186,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -439,11 +445,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -509,31 +524,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -835,19 +859,19 @@
   <cols>
     <col min="1" max="1" width="14.85546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="2.42578125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="10" customWidth="1"/>
     <col min="4" max="4" width="2.42578125" style="9" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="10" customWidth="1"/>
     <col min="6" max="6" width="2.42578125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="3" style="10" customWidth="1"/>
     <col min="8" max="8" width="2.42578125" style="9" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" style="10" customWidth="1"/>
     <col min="10" max="10" width="2.42578125" style="9" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" style="10" customWidth="1"/>
     <col min="12" max="12" width="2.42578125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="2.42578125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="10" customWidth="1"/>
+    <col min="13" max="13" width="14" style="10" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="3.42578125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="43.5" customHeight="1">
@@ -890,7 +914,7 @@
       <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8">
@@ -931,7 +955,7 @@
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A3" s="23"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="8">
         <v>27</v>
       </c>
@@ -970,7 +994,7 @@
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="31" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8">
@@ -1003,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N4" s="8">
         <v>9</v>
@@ -1011,7 +1035,7 @@
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A5" s="23"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="8">
         <v>10</v>
       </c>
@@ -1041,14 +1065,16 @@
       <c r="L5" s="8">
         <v>15</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="N5" s="8">
         <v>16</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A6" s="23"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="8">
         <v>17</v>
       </c>
@@ -1075,17 +1101,19 @@
       <c r="K6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="13">
         <v>22</v>
       </c>
-      <c r="M6" s="6"/>
+      <c r="M6" s="14" t="s">
+        <v>18</v>
+      </c>
       <c r="N6" s="8">
         <v>23</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A7" s="23"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="8">
         <v>24</v>
       </c>
@@ -1106,21 +1134,23 @@
       <c r="I7" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="23">
         <v>28</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="8">
+      <c r="K7" s="32"/>
+      <c r="L7" s="17">
         <v>29</v>
       </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="8">
+      <c r="M7" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="12">
         <v>30</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="8">
@@ -1137,29 +1167,29 @@
         <v>3</v>
       </c>
       <c r="G8" s="11"/>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <v>4</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="24">
         <v>5</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="33">
         <v>6</v>
       </c>
-      <c r="M8" s="6"/>
+      <c r="M8" s="16"/>
       <c r="N8" s="8">
         <v>7</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A9" s="23"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="8">
         <v>8</v>
       </c>
@@ -1180,7 +1210,7 @@
       <c r="I9" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="25">
         <v>12</v>
       </c>
       <c r="K9" s="22" t="s">
@@ -1196,7 +1226,7 @@
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A10" s="23"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="8">
         <v>15</v>
       </c>
@@ -1231,7 +1261,7 @@
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A11" s="23"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="8">
         <v>22</v>
       </c>
@@ -1266,7 +1296,7 @@
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" ht="35.25" customHeight="1">
-      <c r="A12" s="23"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="8">
         <v>29</v>
       </c>
@@ -1303,7 +1333,7 @@
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="31" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="8">
@@ -1342,7 +1372,7 @@
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A14" s="23"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="8">
         <v>12</v>
       </c>
@@ -1363,7 +1393,7 @@
       <c r="I14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="27">
         <v>16</v>
       </c>
       <c r="K14" s="18" t="s">
@@ -1379,7 +1409,7 @@
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A15" s="23"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="8">
         <v>19</v>
       </c>
@@ -1394,16 +1424,16 @@
         <v>21</v>
       </c>
       <c r="G15" s="11"/>
-      <c r="H15" s="27">
+      <c r="H15" s="26">
         <v>22</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="29">
         <v>23</v>
       </c>
-      <c r="K15" s="31" t="s">
+      <c r="K15" s="30" t="s">
         <v>18</v>
       </c>
       <c r="L15" s="8">
@@ -1416,7 +1446,7 @@
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A16" s="23"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="8">
         <v>26</v>
       </c>
@@ -1459,7 +1489,7 @@
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A13:A16"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.34" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>